--- a/nr-cleaning/ig/StructureDefinition-as-address-extended.xlsx
+++ b/nr-cleaning/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T15:04:54+00:00</t>
+    <t>2024-03-06T15:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-cleaning/ig/StructureDefinition-as-address-extended.xlsx
+++ b/nr-cleaning/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T15:16:55+00:00</t>
+    <t>2024-03-06T15:26:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-cleaning/ig/StructureDefinition-as-address-extended.xlsx
+++ b/nr-cleaning/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T15:26:05+00:00</t>
+    <t>2024-03-06T16:31:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
